--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_2.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_2.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>38.94080662727356</v>
+        <v>68.32536339759827</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1431720199493261</v>
+        <v>0.4710107815676722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7628865838050842</v>
+        <v>0.8505747318267822</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7347995042800903</v>
+        <v>0.7755627036094666</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7096307277679443</v>
+        <v>0.7272727489471436</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7088791728019714</v>
+        <v>0.7333333492279053</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1010807678103447</v>
+        <v>0.1875420063734054</v>
       </c>
       <c r="K2" t="n">
-        <v>19.6290807723999</v>
+        <v>67.0149097442627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0598593473434448</v>
+        <v>0.1192883920669555</v>
       </c>
       <c r="M2" t="n">
-        <v>0.110951075553894</v>
+        <v>0.5007438611984253</v>
       </c>
       <c r="N2" t="n">
-        <v>0.115096321105957</v>
+        <v>0.2038124990463256</v>
       </c>
       <c r="O2" t="n">
-        <v>2.992967367172241</v>
+        <v>5.964419603347778</v>
       </c>
       <c r="P2" t="n">
-        <v>5.547553777694702</v>
+        <v>25.03719305992126</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.754816055297852</v>
+        <v>10.19062495231628</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-160229</t>
+          <t>20250725-223619</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>31.10494256019592</v>
+        <v>103.3557612895966</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>15.44999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.146933092639364</v>
+        <v>0.4718476818366484</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8478260636329651</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7178549766540527</v>
+        <v>0.7964033484458923</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7055476307868958</v>
+        <v>0.7241118550300598</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7062986493110657</v>
+        <v>0.7246596217155457</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0994821190834045</v>
+        <v>0.187396302819252</v>
       </c>
       <c r="K3" t="n">
-        <v>14.10325837135315</v>
+        <v>55.56255292892456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0607071161270141</v>
+        <v>0.1145238780975341</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1181252527236938</v>
+        <v>0.496018385887146</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1207747030258178</v>
+        <v>0.2029150152206421</v>
       </c>
       <c r="O3" t="n">
-        <v>3.035355806350708</v>
+        <v>5.726193904876709</v>
       </c>
       <c r="P3" t="n">
-        <v>5.906262636184692</v>
+        <v>24.8009192943573</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.038735151290894</v>
+        <v>10.1457507610321</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-160421</t>
+          <t>20250725-224006</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>62.48103547096253</v>
+        <v>113.6465871334076</v>
       </c>
       <c r="D4" t="n">
-        <v>6.519999980926514</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1450334945693611</v>
+        <v>0.471166869815515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8409090638160706</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.760617733001709</v>
+        <v>0.7909319996833801</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6640190482139587</v>
+        <v>0.7622478604316711</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6656076312065125</v>
+        <v>0.7670251131057739</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0873725637793541</v>
+        <v>0.1833884418010711</v>
       </c>
       <c r="K4" t="n">
-        <v>19.34668064117432</v>
+        <v>59.03408432006836</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0598899126052856</v>
+        <v>0.1005816745758056</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1108040046691894</v>
+        <v>0.4915605783462524</v>
       </c>
       <c r="N4" t="n">
-        <v>0.119082384109497</v>
+        <v>0.2046522760391235</v>
       </c>
       <c r="O4" t="n">
-        <v>2.994495630264282</v>
+        <v>5.029083728790283</v>
       </c>
       <c r="P4" t="n">
-        <v>5.540200233459473</v>
+        <v>24.57802891731263</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.954119205474854</v>
+        <v>10.23261380195618</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-160601</t>
+          <t>20250725-224416</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>76.82273435592651</v>
+        <v>102.2926726341248</v>
       </c>
       <c r="D5" t="n">
-        <v>6.519999980926514</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1453017875363554</v>
+        <v>0.4723328744823282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8695651888847351</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7861799001693726</v>
+        <v>0.7923280596733093</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7447272539138794</v>
+        <v>0.7422680258750916</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7371512651443481</v>
+        <v>0.7394834160804749</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1666375398635864</v>
+        <v>0.181598275899887</v>
       </c>
       <c r="K5" t="n">
-        <v>19.35775232315063</v>
+        <v>61.85993599891663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0709398889541626</v>
+        <v>0.1039079093933105</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1116385126113891</v>
+        <v>0.493601541519165</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1151805782318115</v>
+        <v>0.2070105600357055</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54699444770813</v>
+        <v>5.195395469665527</v>
       </c>
       <c r="P5" t="n">
-        <v>5.581925630569458</v>
+        <v>24.68007707595825</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.759028911590576</v>
+        <v>10.35052800178528</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-160817</t>
+          <t>20250725-224838</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>59.37403678894043</v>
+        <v>67.75055766105652</v>
       </c>
       <c r="D6" t="n">
-        <v>6.519999980926514</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1462286306639848</v>
+        <v>0.4693167332945199</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8372092843055725</v>
+        <v>0.8351648449897766</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7691247463226318</v>
+        <v>0.7934585213661194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7260479331016541</v>
+        <v>0.7194570302963257</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7274085283279419</v>
+        <v>0.7160120606422424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0807815194129943</v>
+        <v>0.1819461286067962</v>
       </c>
       <c r="K6" t="n">
-        <v>19.74275803565979</v>
+        <v>60.7056987285614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.065195026397705</v>
+        <v>0.106474871635437</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1070601511001587</v>
+        <v>0.5010016298294068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1179280424118042</v>
+        <v>0.212454981803894</v>
       </c>
       <c r="O6" t="n">
-        <v>3.259751319885254</v>
+        <v>5.323743581771851</v>
       </c>
       <c r="P6" t="n">
-        <v>5.353007555007935</v>
+        <v>25.05008149147034</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.89640212059021</v>
+        <v>10.6227490901947</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-161047</t>
+          <t>20250725-225252</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>96.50108742713928</v>
+        <v>523.2854816913605</v>
       </c>
       <c r="D2" t="n">
-        <v>9.800000190734863</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.288075088902756</v>
+        <v>0.5504273841014276</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8539325594902039</v>
+        <v>0.804347813129425</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7984933853149414</v>
+        <v>0.7182539701461792</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7880434989929199</v>
+        <v>0.6980999112129211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7869299054145813</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1249960735440254</v>
+        <v>0.1318091601133346</v>
       </c>
       <c r="K2" t="n">
-        <v>87.45012521743774</v>
+        <v>76.42565965652466</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1098069047927856</v>
+        <v>0.1148067045211791</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5020783853530884</v>
+        <v>0.2400709295272827</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2009978723526001</v>
+        <v>0.2245742034912109</v>
       </c>
       <c r="O2" t="n">
-        <v>5.490345239639282</v>
+        <v>5.74033522605896</v>
       </c>
       <c r="P2" t="n">
-        <v>25.10391926765442</v>
+        <v>12.00354647636414</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.04989361763</v>
+        <v>11.22871017456055</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-060400</t>
+          <t>20250724-151722</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>44.82296633720398</v>
+        <v>558.9244031906128</v>
       </c>
       <c r="D3" t="n">
-        <v>9.760000228881836</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2908365813394387</v>
+        <v>0.5174402473629385</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8314606547355652</v>
+        <v>0.875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7839388251304626</v>
+        <v>0.8319900631904602</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7831632494926453</v>
+        <v>0.833737850189209</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7892720103263855</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1240054443478584</v>
+        <v>0.1359405368566513</v>
       </c>
       <c r="K3" t="n">
-        <v>95.82262706756592</v>
+        <v>76.06761693954468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1053673124313354</v>
+        <v>0.1100910425186157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49586501121521</v>
+        <v>0.2416387891769409</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2034552288055419</v>
+        <v>0.2096806049346923</v>
       </c>
       <c r="O3" t="n">
-        <v>5.268365621566772</v>
+        <v>5.504552125930786</v>
       </c>
       <c r="P3" t="n">
-        <v>24.79325056076049</v>
+        <v>12.08193945884705</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.1727614402771</v>
+        <v>10.48403024673462</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-060836</t>
+          <t>20250724-152847</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C4" t="n">
-        <v>62.72775912284851</v>
+        <v>627.5504400730133</v>
       </c>
       <c r="D4" t="n">
-        <v>9.779999732971191</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2904422879219055</v>
+        <v>0.5268132220476102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8602150678634644</v>
+        <v>0.9032257795333862</v>
       </c>
       <c r="G4" t="n">
-        <v>0.778514564037323</v>
+        <v>0.8540145754814148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7472687363624573</v>
+        <v>0.8479999899864197</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7446964383125305</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1576692461967468</v>
+        <v>0.1368939727544784</v>
       </c>
       <c r="K4" t="n">
-        <v>91.83449268341064</v>
+        <v>76.77650570869446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1314001178741455</v>
+        <v>0.1190731763839721</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4980360889434814</v>
+        <v>0.2495586776733398</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2072589778900146</v>
+        <v>0.2238975763320922</v>
       </c>
       <c r="O4" t="n">
-        <v>6.570005893707275</v>
+        <v>5.953658819198608</v>
       </c>
       <c r="P4" t="n">
-        <v>24.90180444717407</v>
+        <v>12.47793388366699</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.36294889450073</v>
+        <v>11.19487881660461</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-061228</t>
+          <t>20250724-154102</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>76.85365629196167</v>
+        <v>513.2379102706909</v>
       </c>
       <c r="D5" t="n">
-        <v>9.800000190734863</v>
+        <v>19.43000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.290230274877765</v>
+        <v>0.5509562858792602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8723404407501221</v>
+        <v>0.8478260636329651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7816393375396729</v>
+        <v>0.8036585450172424</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7819253206253052</v>
+        <v>0.7783783674240112</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7808662056922913</v>
+        <v>0.7704917788505554</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1296377331018448</v>
+        <v>0.1364048719406128</v>
       </c>
       <c r="K5" t="n">
-        <v>79.3204870223999</v>
+        <v>81.83622241020203</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1161284589767456</v>
+        <v>0.1183341073989868</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4966540241241455</v>
+        <v>0.2409216833114624</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2077931213378906</v>
+        <v>0.2342004346847534</v>
       </c>
       <c r="O5" t="n">
-        <v>5.80642294883728</v>
+        <v>5.916705369949341</v>
       </c>
       <c r="P5" t="n">
-        <v>24.83270120620728</v>
+        <v>12.04608416557312</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.38965606689453</v>
+        <v>11.71002173423767</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-061635</t>
+          <t>20250724-155412</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C6" t="n">
-        <v>87.05446434020996</v>
+        <v>613.0870063304901</v>
       </c>
       <c r="D6" t="n">
-        <v>9.810000419616699</v>
+        <v>20.65999984741211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.290089444846523</v>
+        <v>0.5380379482110341</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.901098906993866</v>
       </c>
       <c r="G6" t="n">
-        <v>0.802049994468689</v>
+        <v>0.8360863924026489</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7701067328453064</v>
+        <v>0.8350649476051331</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7692307829856873</v>
+        <v>0.8370565176010132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1288010627031326</v>
+        <v>0.1301178336143493</v>
       </c>
       <c r="K6" t="n">
-        <v>81.88476848602295</v>
+        <v>82.36298227310181</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1049525356292724</v>
+        <v>0.1134463834762573</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4909066200256348</v>
+        <v>0.2460176229476928</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1983826494216919</v>
+        <v>0.238872013092041</v>
       </c>
       <c r="O6" t="n">
-        <v>5.247626781463623</v>
+        <v>5.672319173812866</v>
       </c>
       <c r="P6" t="n">
-        <v>24.54533100128174</v>
+        <v>12.30088114738464</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.919132471084597</v>
+        <v>11.94360065460205</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-062043</t>
+          <t>20250724-160543</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4454,53 +4454,53 @@
         <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>474.1817770004273</v>
+        <v>386.2577726840973</v>
       </c>
       <c r="D2" t="n">
-        <v>14.23999977111816</v>
+        <v>9.989999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4860777373115221</v>
+        <v>0.4750929032762845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9052631855010986</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8435207605361938</v>
+        <v>0.7161159515380859</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8280423283576965</v>
+        <v>0.698847234249115</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8195187449455261</v>
+        <v>0.700434148311615</v>
       </c>
       <c r="J2" t="n">
-        <v>0.123533010482788</v>
+        <v>0.1544519960880279</v>
       </c>
       <c r="K2" t="n">
-        <v>76.44016885757446</v>
+        <v>70.76026177406311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1160155248641967</v>
+        <v>0.1217930078506469</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2385981082916259</v>
+        <v>0.2562768602371216</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2285906267166137</v>
+        <v>0.2156467008590698</v>
       </c>
       <c r="O2" t="n">
-        <v>5.800776243209839</v>
+        <v>6.089650392532349</v>
       </c>
       <c r="P2" t="n">
-        <v>11.9299054145813</v>
+        <v>12.81384301185608</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.42953133583069</v>
+        <v>10.78233504295349</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-121906</t>
+          <t>20250727-005100</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>487.5823211669922</v>
+        <v>306.5334253311157</v>
       </c>
       <c r="D3" t="n">
-        <v>14.53999996185303</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4683725829162294</v>
+        <v>0.5227560776731243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8791208863258362</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8221820592880249</v>
+        <v>0.6986111402511597</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7897648811340332</v>
+        <v>0.6866325736045837</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7899860739707947</v>
+        <v>0.3309929668903351</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1376935988664627</v>
+        <v>0.1538443267345428</v>
       </c>
       <c r="K3" t="n">
-        <v>82.32498717308044</v>
+        <v>66.89497137069702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1121058130264282</v>
+        <v>0.1174062967300415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2364079236984252</v>
+        <v>0.2647739839553833</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2274882507324218</v>
+        <v>0.2024920654296875</v>
       </c>
       <c r="O3" t="n">
-        <v>5.605290651321411</v>
+        <v>5.870314836502075</v>
       </c>
       <c r="P3" t="n">
-        <v>11.82039618492126</v>
+        <v>13.23869919776916</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.37441253662109</v>
+        <v>10.12460327148438</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-122958</t>
+          <t>20250727-010010</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>470.9862282276154</v>
+        <v>398.351711511612</v>
       </c>
       <c r="D4" t="n">
-        <v>14.13000011444092</v>
+        <v>10.25</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4720240583864309</v>
+        <v>0.5654125927851118</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7191011309623718</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5015337467193604</v>
+        <v>0.4569536447525024</v>
       </c>
       <c r="H4" t="n">
-        <v>0.449999988079071</v>
+        <v>0.4558697640895843</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.3887850344181061</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1279652565717697</v>
+        <v>0.1539456844329834</v>
       </c>
       <c r="K4" t="n">
-        <v>82.66237878799438</v>
+        <v>69.44494771957397</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1138921642303466</v>
+        <v>0.1142220020294189</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2275731182098388</v>
+        <v>0.2522146701812744</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2188972759246826</v>
+        <v>0.2097018909454345</v>
       </c>
       <c r="O4" t="n">
-        <v>5.694608211517334</v>
+        <v>5.711100101470947</v>
       </c>
       <c r="P4" t="n">
-        <v>11.37865591049194</v>
+        <v>12.61073350906372</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.94486379623413</v>
+        <v>10.48509454727173</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-124104</t>
+          <t>20250727-010755</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>498.7253224849701</v>
+        <v>331.4193778038025</v>
       </c>
       <c r="D5" t="n">
-        <v>14.51000022888184</v>
+        <v>9.670000076293944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4956133526856782</v>
+        <v>0.5601106727001618</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8505747318267822</v>
+        <v>0.6428571343421936</v>
       </c>
       <c r="G5" t="n">
-        <v>0.790123462677002</v>
+        <v>0.390581727027893</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7586685419082642</v>
+        <v>0.3475046157836914</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0451306402683258</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1189293265342712</v>
+        <v>0.1437510550022125</v>
       </c>
       <c r="K5" t="n">
-        <v>82.92569780349731</v>
+        <v>64.08114981651306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1210698747634887</v>
+        <v>0.1083275318145751</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2347463274002075</v>
+        <v>0.2526172065734863</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2188994121551513</v>
+        <v>0.1953708124160766</v>
       </c>
       <c r="O5" t="n">
-        <v>6.053493738174439</v>
+        <v>5.41637659072876</v>
       </c>
       <c r="P5" t="n">
-        <v>11.73731637001038</v>
+        <v>12.63086032867432</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.94497060775757</v>
+        <v>9.768540620803831</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-125151</t>
+          <t>20250727-011714</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>467.1913273334503</v>
+        <v>411.6671462059021</v>
       </c>
       <c r="D6" t="n">
-        <v>14.52999973297119</v>
+        <v>10.09000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4802358562747637</v>
+        <v>0.5712755791476516</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8958333134651184</v>
+        <v>0.8764045238494873</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8393194675445557</v>
+        <v>0.8073278665542603</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8400746583938599</v>
+        <v>0.7660167217254639</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.3687258660793304</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1313115358352661</v>
+        <v>0.1561851054430008</v>
       </c>
       <c r="K6" t="n">
-        <v>82.814204454422</v>
+        <v>57.52774834632874</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1086674928665161</v>
+        <v>0.1199944877624511</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2509119939804077</v>
+        <v>0.2671390390396118</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2169447612762451</v>
+        <v>0.1998950052261352</v>
       </c>
       <c r="O6" t="n">
-        <v>5.433374643325806</v>
+        <v>5.999724388122559</v>
       </c>
       <c r="P6" t="n">
-        <v>12.54559969902039</v>
+        <v>13.35695195198059</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.84723806381226</v>
+        <v>9.994750261306764</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-130307</t>
+          <t>20250727-012526</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>269.3096687793732</v>
+        <v>297.5734970569611</v>
       </c>
       <c r="D2" t="n">
-        <v>9.420000076293944</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4520771780679392</v>
+        <v>0.377199022927218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5479452013969421</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3240973949432373</v>
+        <v>0.6904109716415405</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2358974367380142</v>
+        <v>0.6841741800308228</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.4805531501770019</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1358292400836944</v>
+        <v>0.1008778288960456</v>
       </c>
       <c r="K2" t="n">
-        <v>69.25777363777161</v>
+        <v>25.45613026618957</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1238365650177002</v>
+        <v>0.08139573097229</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2464201068878173</v>
+        <v>0.1181022214889526</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2042230701446533</v>
+        <v>0.1205093383789062</v>
       </c>
       <c r="O2" t="n">
-        <v>6.19182825088501</v>
+        <v>4.069786548614502</v>
       </c>
       <c r="P2" t="n">
-        <v>12.32100534439087</v>
+        <v>5.905111074447632</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.21115350723267</v>
+        <v>6.025466918945312</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-021235</t>
+          <t>20250728-045120</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>305.8010213375092</v>
+        <v>211.0540277957916</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5355375808748332</v>
+        <v>0.361022216854272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8791208863258362</v>
+        <v>0.6972476840019226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7693266868591309</v>
+        <v>0.633952260017395</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7505126595497131</v>
+        <v>0.6269429922103882</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6260111927986145</v>
+        <v>0.6255677938461304</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1289566755294799</v>
+        <v>0.110750563442707</v>
       </c>
       <c r="K3" t="n">
-        <v>63.74764657020569</v>
+        <v>19.75497651100159</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1398194646835327</v>
+        <v>0.0924582815170288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2597723722457886</v>
+        <v>0.1304887676239013</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2222238636016845</v>
+        <v>0.1333829927444458</v>
       </c>
       <c r="O3" t="n">
-        <v>6.990973234176636</v>
+        <v>4.62291407585144</v>
       </c>
       <c r="P3" t="n">
-        <v>12.98861861228943</v>
+        <v>6.524438381195068</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.11119318008423</v>
+        <v>6.66914963722229</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-021951</t>
+          <t>20250728-045743</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>302.1422457695007</v>
+        <v>249.7508292198181</v>
       </c>
       <c r="D4" t="n">
-        <v>9.180000305175779</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5691653694524321</v>
+        <v>0.3837515970722573</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8172042965888977</v>
+        <v>0.7954545617103577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7739018201828003</v>
+        <v>0.7248677015304565</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6961740255355835</v>
+        <v>0.6879169940948486</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6552529335021973</v>
+        <v>0.4158043265342712</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1355792582035064</v>
+        <v>0.1758098602294922</v>
       </c>
       <c r="K4" t="n">
-        <v>67.01540184020996</v>
+        <v>25.24104738235474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1199521589279174</v>
+        <v>0.1031110095977783</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2631611728668213</v>
+        <v>0.1114790678024292</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2240669631958007</v>
+        <v>0.1144700622558593</v>
       </c>
       <c r="O4" t="n">
-        <v>5.997607946395874</v>
+        <v>5.155550479888916</v>
       </c>
       <c r="P4" t="n">
-        <v>13.15805864334106</v>
+        <v>5.57395339012146</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.20334815979004</v>
+        <v>5.723503112792969</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-022734</t>
+          <t>20250728-050</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>329.5157883167267</v>
+        <v>210.3790075778961</v>
       </c>
       <c r="D5" t="n">
-        <v>8.960000038146973</v>
+        <v>5.320000171661377</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5429165267075101</v>
+        <v>0.4182010347745856</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.6590909361839294</v>
       </c>
       <c r="G5" t="n">
-        <v>0.777437150478363</v>
+        <v>0.5679163932800293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7446067929267883</v>
+        <v>0.4884792566299438</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4261992573738098</v>
+        <v>0.5069767236709595</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1324523985385894</v>
+        <v>0.1122760400176048</v>
       </c>
       <c r="K5" t="n">
-        <v>58.62139129638672</v>
+        <v>20.35852861404419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1226022815704345</v>
+        <v>0.09141543865203849</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2679150390625</v>
+        <v>0.1164189100265502</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2174985647201538</v>
+        <v>0.1242113208770751</v>
       </c>
       <c r="O5" t="n">
-        <v>6.130114078521729</v>
+        <v>4.570771932601929</v>
       </c>
       <c r="P5" t="n">
-        <v>13.395751953125</v>
+        <v>5.820945501327515</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.87492823600769</v>
+        <v>6.21056604385376</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-023505</t>
+          <t>20250728-051102</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>294.7414102554321</v>
+        <v>372.4171552658081</v>
       </c>
       <c r="D6" t="n">
-        <v>9.229999542236328</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5910062518986788</v>
+        <v>0.4619984689606241</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9052631855010986</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="G6" t="n">
-        <v>0.816575288772583</v>
+        <v>0.7127659320831299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8115384578704834</v>
+        <v>0.6789125800132751</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7270194888114929</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1344536542892456</v>
+        <v>0.1017532348632812</v>
       </c>
       <c r="K6" t="n">
-        <v>61.34621453285217</v>
+        <v>20.21776509284973</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1308464336395263</v>
+        <v>0.0900384330749511</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2621458578109741</v>
+        <v>0.1180573272705078</v>
       </c>
       <c r="N6" t="n">
-        <v>0.209354658126831</v>
+        <v>0.1127647399902343</v>
       </c>
       <c r="O6" t="n">
-        <v>6.542321681976318</v>
+        <v>4.501921653747559</v>
       </c>
       <c r="P6" t="n">
-        <v>13.10729289054871</v>
+        <v>5.902866363525391</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.46773290634155</v>
+        <v>5.638236999511719</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-024257</t>
+          <t>20250728-051600</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>204.6818625926972</v>
+        <v>261.9421565532684</v>
       </c>
       <c r="D2" t="n">
-        <v>3.119999885559082</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3702400404214859</v>
+        <v>0.4416808494419422</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7789473533630371</v>
+        <v>0.8505747318267822</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7458745837211609</v>
+        <v>0.7735602259635925</v>
       </c>
       <c r="H2" t="n">
-        <v>0.740094006061554</v>
+        <v>0.7234678864479065</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7305874228477478</v>
+        <v>0.708364725112915</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1270026117563247</v>
+        <v>0.1149011775851249</v>
       </c>
       <c r="K2" t="n">
-        <v>29.82793116569519</v>
+        <v>34.57914805412292</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0940403079986572</v>
+        <v>0.09387264251708979</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1190372991561889</v>
+        <v>0.1892691564559936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1274533700942993</v>
+        <v>0.1831696319580078</v>
       </c>
       <c r="O2" t="n">
-        <v>4.702015399932861</v>
+        <v>4.693632125854492</v>
       </c>
       <c r="P2" t="n">
-        <v>5.951864957809448</v>
+        <v>9.463457822799684</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.372668504714966</v>
+        <v>9.158481597900391</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-170437</t>
+          <t>20250729-082224</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>182.2201678752899</v>
+        <v>278.6654801368713</v>
       </c>
       <c r="D3" t="n">
-        <v>3.049999952316284</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3754829012534835</v>
+        <v>0.446565919843587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.717391312122345</v>
+        <v>0.8602150678634644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6186699271202087</v>
+        <v>0.8325358629226685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6172506809234619</v>
+        <v>0.8289557695388794</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3681085705757141</v>
+        <v>0.8212684392929077</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1127786338329315</v>
+        <v>0.1211898922920227</v>
       </c>
       <c r="K3" t="n">
-        <v>32.08378577232361</v>
+        <v>39.67870259284973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0918760156631469</v>
+        <v>0.0985569047927856</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1193585300445556</v>
+        <v>0.1847918272018432</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1189907836914062</v>
+        <v>0.1789094018936157</v>
       </c>
       <c r="O3" t="n">
-        <v>4.593800783157349</v>
+        <v>4.927845239639282</v>
       </c>
       <c r="P3" t="n">
-        <v>5.967926502227783</v>
+        <v>9.239591360092165</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.949539184570312</v>
+        <v>8.945470094680786</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-170933</t>
+          <t>20250729-082837</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>195.6219255924225</v>
+        <v>272.4946632385254</v>
       </c>
       <c r="D4" t="n">
-        <v>3.25</v>
+        <v>7.760000228881836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3941211079029327</v>
+        <v>0.4574311256408691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8351648449897766</v>
+        <v>0.804347813129425</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7779862284660339</v>
+        <v>0.77667635679245</v>
       </c>
       <c r="H4" t="n">
-        <v>0.732846736907959</v>
+        <v>0.7685123682022095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7179867029190063</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1375268399715423</v>
+        <v>0.1320007890462875</v>
       </c>
       <c r="K4" t="n">
-        <v>26.43934893608093</v>
+        <v>40.40009903907776</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0963350009918213</v>
+        <v>0.0957796621322631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1165920734405517</v>
+        <v>0.1826136016845703</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1247454452514648</v>
+        <v>0.1685219001770019</v>
       </c>
       <c r="O4" t="n">
-        <v>4.816750049591064</v>
+        <v>4.788983106613159</v>
       </c>
       <c r="P4" t="n">
-        <v>5.829603672027588</v>
+        <v>9.130680084228516</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.237272262573242</v>
+        <v>8.426095008850098</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-171408</t>
+          <t>20250729-083510</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>181.2209594249725</v>
+        <v>258.5119993686676</v>
       </c>
       <c r="D5" t="n">
-        <v>2.910000085830688</v>
+        <v>7.059999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.431917077233625</v>
+        <v>0.4538303382542668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8045976758003235</v>
+        <v>0.8247422575950623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7724049091339111</v>
+        <v>0.7567901015281677</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6937835812568665</v>
+        <v>0.7180966138839722</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3084780275821686</v>
+        <v>0.1969697028398513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.134818434715271</v>
+        <v>0.1175998374819755</v>
       </c>
       <c r="K5" t="n">
-        <v>33.32186007499695</v>
+        <v>34.56107521057129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0888459587097168</v>
+        <v>0.09485357284545889</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1148325967788696</v>
+        <v>0.1753862476348877</v>
       </c>
       <c r="N5" t="n">
-        <v>0.113976559638977</v>
+        <v>0.1773213243484497</v>
       </c>
       <c r="O5" t="n">
-        <v>4.44229793548584</v>
+        <v>4.742678642272949</v>
       </c>
       <c r="P5" t="n">
-        <v>5.741629838943481</v>
+        <v>8.769312381744385</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.698827981948853</v>
+        <v>8.866066217422485</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-171851</t>
+          <t>20250729-084137</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C6" t="n">
-        <v>184.9486570358276</v>
+        <v>368.4462413787842</v>
       </c>
       <c r="D6" t="n">
-        <v>3.150000095367432</v>
+        <v>7.269999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4525044202804565</v>
+        <v>0.4766784099737803</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7083333134651184</v>
+        <v>0.875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6273062825202942</v>
+        <v>0.7990314960479736</v>
       </c>
       <c r="H6" t="n">
-        <v>0.616847813129425</v>
+        <v>0.7918968796730042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6158038377761841</v>
+        <v>0.7885215282440186</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1183588877320289</v>
+        <v>0.1299896538257599</v>
       </c>
       <c r="K6" t="n">
-        <v>33.21500492095947</v>
+        <v>34.18179845809937</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1024248456954956</v>
+        <v>0.0990040683746337</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1223306465148925</v>
+        <v>0.1885566616058349</v>
       </c>
       <c r="N6" t="n">
-        <v>0.12711021900177</v>
+        <v>0.1952591943740844</v>
       </c>
       <c r="O6" t="n">
-        <v>5.12124228477478</v>
+        <v>4.950203418731689</v>
       </c>
       <c r="P6" t="n">
-        <v>6.116532325744629</v>
+        <v>9.427833080291748</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.355510950088501</v>
+        <v>9.762959718704224</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-172325</t>
+          <t>20250729-084741</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>217.0850231647492</v>
+        <v>126.0958859920502</v>
       </c>
       <c r="D2" t="n">
-        <v>7.039999961853027</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4523637332888536</v>
+        <v>0.1388313678048905</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8695651888847351</v>
+        <v>0.7727272510528564</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7817509174346924</v>
+        <v>0.6563944816589355</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7615804076194763</v>
+        <v>0.6569005250930786</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.6537567973136902</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1243939995765686</v>
+        <v>0.0888940691947937</v>
       </c>
       <c r="K2" t="n">
-        <v>40.34337759017944</v>
+        <v>8.694010496139526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1147664546966552</v>
+        <v>0.0657349109649658</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1751124048233032</v>
+        <v>0.08320023059844971</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1636475276947021</v>
+        <v>0.08328419685363769</v>
       </c>
       <c r="O2" t="n">
-        <v>5.738322734832764</v>
+        <v>3.286745548248291</v>
       </c>
       <c r="P2" t="n">
-        <v>8.755620241165161</v>
+        <v>4.160011529922485</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.182376384735107</v>
+        <v>4.164209842681885</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-050955</t>
+          <t>20250730-085046</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>235.8285455703736</v>
+        <v>132.3336021900177</v>
       </c>
       <c r="D3" t="n">
-        <v>5.960000038146973</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4335403925842709</v>
+        <v>0.1394678148325909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8723404407501221</v>
+        <v>0.7326732873916626</v>
       </c>
       <c r="G3" t="n">
-        <v>0.833231508731842</v>
+        <v>0.6696100234985352</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8257817625999451</v>
+        <v>0.6705968976020813</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7106825113296509</v>
+        <v>0.6686260104179382</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1011203005909919</v>
+        <v>0.1052653044462204</v>
       </c>
       <c r="K3" t="n">
-        <v>40.03080558776856</v>
+        <v>8.646347284317017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1041268491744995</v>
+        <v>0.06397952556610099</v>
       </c>
       <c r="M3" t="n">
-        <v>0.181756329536438</v>
+        <v>0.08839242458343501</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1759812498092651</v>
+        <v>0.0982712507247924</v>
       </c>
       <c r="O3" t="n">
-        <v>5.206342458724976</v>
+        <v>3.198976278305054</v>
       </c>
       <c r="P3" t="n">
-        <v>9.087816476821899</v>
+        <v>4.419621229171753</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.799062490463257</v>
+        <v>4.913562536239624</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-051529</t>
+          <t>20250730-085352</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>217.9542486667633</v>
+        <v>88.82174372673035</v>
       </c>
       <c r="D4" t="n">
-        <v>6.820000171661377</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4721066009166629</v>
+        <v>0.1386496851504859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8235294222831726</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7866004705429077</v>
+        <v>0.6719310879707336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7214815020561218</v>
+        <v>0.6691842675209045</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6246973276138306</v>
+        <v>0.6701966524124146</v>
       </c>
       <c r="J4" t="n">
-        <v>0.132449209690094</v>
+        <v>0.07802152633666989</v>
       </c>
       <c r="K4" t="n">
-        <v>34.45823264122009</v>
+        <v>13.95470666885376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1047895431518554</v>
+        <v>0.07198141098022461</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1927403116226196</v>
+        <v>0.08589851379394529</v>
       </c>
       <c r="N4" t="n">
-        <v>0.184093427658081</v>
+        <v>0.0863818931579589</v>
       </c>
       <c r="O4" t="n">
-        <v>5.239477157592773</v>
+        <v>3.59907054901123</v>
       </c>
       <c r="P4" t="n">
-        <v>9.63701558113098</v>
+        <v>4.294925689697266</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.204671382904053</v>
+        <v>4.319094657897949</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-052121</t>
+          <t>20250730-085655</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>233.0989134311676</v>
+        <v>89.8173942565918</v>
       </c>
       <c r="D5" t="n">
-        <v>5.949999809265137</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5140366444985072</v>
+        <v>0.1391080125408657</v>
       </c>
       <c r="F5" t="n">
-        <v>0.791208803653717</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G5" t="n">
-        <v>0.774233877658844</v>
+        <v>0.6710144877433777</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7231638431549072</v>
+        <v>0.6558891534805298</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6931982636451721</v>
+        <v>0.6584043502807617</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1148333474993705</v>
+        <v>0.0866167172789573</v>
       </c>
       <c r="K5" t="n">
-        <v>64.75300431251526</v>
+        <v>14.05317401885986</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1034556198120117</v>
+        <v>0.0720649576187133</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1901737785339355</v>
+        <v>0.08589765548706051</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1764404201507568</v>
+        <v>0.0838581752777099</v>
       </c>
       <c r="O5" t="n">
-        <v>5.172780990600586</v>
+        <v>3.603247880935669</v>
       </c>
       <c r="P5" t="n">
-        <v>9.508688926696776</v>
+        <v>4.294882774353027</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.822021007537842</v>
+        <v>4.192908763885498</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-052651</t>
+          <t>20250730-085923</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>214.6229648590088</v>
+        <v>89.23352980613708</v>
       </c>
       <c r="D6" t="n">
-        <v>6.429999828338623</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.53848808484022</v>
+        <v>0.1388488116405777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8260869383811951</v>
+        <v>0.8181818127632141</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7353144288063049</v>
+        <v>0.6538461446762085</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7289325594902039</v>
+        <v>0.6503816843032837</v>
       </c>
       <c r="I6" t="n">
-        <v>0.680757999420166</v>
+        <v>0.6407464742660522</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1184926778078079</v>
+        <v>0.0822156742215156</v>
       </c>
       <c r="K6" t="n">
-        <v>62.357008934021</v>
+        <v>14.06033301353455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1062048530578613</v>
+        <v>0.0688987970352172</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1926998996734619</v>
+        <v>0.0851325416564941</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2089582204818725</v>
+        <v>0.0832323312759399</v>
       </c>
       <c r="O6" t="n">
-        <v>5.310242652893066</v>
+        <v>3.444939851760864</v>
       </c>
       <c r="P6" t="n">
-        <v>9.634994983673096</v>
+        <v>4.256627082824707</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.44791102409363</v>
+        <v>4.161616563796997</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-053306</t>
+          <t>20250730-090153</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
-        <v>97.60025143623352</v>
+        <v>99.54995489120483</v>
       </c>
       <c r="D2" t="n">
-        <v>1.740000009536743</v>
+        <v>13.67000007629394</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1341763613431641</v>
+        <v>0.2570470109365989</v>
       </c>
       <c r="F2" t="n">
-        <v>0.901098906993866</v>
+        <v>0.8539325594902039</v>
       </c>
       <c r="G2" t="n">
-        <v>0.797650158405304</v>
+        <v>0.8274509906768799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7751519083976746</v>
+        <v>0.8030619621276855</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7863818407058716</v>
+        <v>0.8120300769805908</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0686486735939979</v>
+        <v>0.09242776036262509</v>
       </c>
       <c r="K2" t="n">
-        <v>15.97784423828125</v>
+        <v>29.77609348297119</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0821577024459838</v>
+        <v>0.0686784029006958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09360282421112059</v>
+        <v>0.1697593116760254</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1054264307022094</v>
+        <v>0.1307783889770507</v>
       </c>
       <c r="O2" t="n">
-        <v>4.107885122299194</v>
+        <v>3.43392014503479</v>
       </c>
       <c r="P2" t="n">
-        <v>4.68014121055603</v>
+        <v>8.48796558380127</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.271321535110474</v>
+        <v>6.538919448852539</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-183539</t>
+          <t>20250731-014212</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>88.69244909286499</v>
+        <v>86.23900437355042</v>
       </c>
       <c r="D3" t="n">
-        <v>1.710000038146973</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1370802881974207</v>
+        <v>0.2568112207671343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8372092843055725</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8079951405525208</v>
+        <v>0.8514251112937927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6564268469810486</v>
+        <v>0.8257006406784058</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6504064798355103</v>
+        <v>0.8254180550575256</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07012758404016491</v>
+        <v>0.0945687294006347</v>
       </c>
       <c r="K3" t="n">
-        <v>15.55081009864807</v>
+        <v>30.37531113624573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0826942205429077</v>
+        <v>0.077179274559021</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09040206909179679</v>
+        <v>0.1638806343078613</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0980330896377563</v>
+        <v>0.1524389791488647</v>
       </c>
       <c r="O3" t="n">
-        <v>4.134711027145386</v>
+        <v>3.85896372795105</v>
       </c>
       <c r="P3" t="n">
-        <v>4.520103454589844</v>
+        <v>8.194031715393066</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.901654481887817</v>
+        <v>7.621948957443237</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-183823</t>
+          <t>20250731-014522</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>66.87515258789062</v>
+        <v>118.6612029075623</v>
       </c>
       <c r="D4" t="n">
-        <v>1.710000038146973</v>
+        <v>13.60999965667725</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1350593031462976</v>
+        <v>0.2568189601103465</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8399999737739563</v>
+        <v>0.8695651888847351</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7938271760940552</v>
+        <v>0.8611793518066406</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7900311350822449</v>
+        <v>0.8667871952056885</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7949367165565491</v>
+        <v>0.8598574995994568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0930452644824981</v>
+        <v>0.10318523645401</v>
       </c>
       <c r="K4" t="n">
-        <v>15.31155633926392</v>
+        <v>30.33361768722535</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08335073947906491</v>
+        <v>0.0702477025985717</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1010682487487793</v>
+        <v>0.1671881914138794</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1061695051193237</v>
+        <v>0.136411337852478</v>
       </c>
       <c r="O4" t="n">
-        <v>4.167536973953247</v>
+        <v>3.512385129928589</v>
       </c>
       <c r="P4" t="n">
-        <v>5.053412437438965</v>
+        <v>8.35940957069397</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.308475255966187</v>
+        <v>6.820566892623901</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-184057</t>
+          <t>20250731-014811</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>49.76188492774963</v>
+        <v>86.66693472862244</v>
       </c>
       <c r="D5" t="n">
-        <v>1.710000038146973</v>
+        <v>13.67000007629394</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1329132526774297</v>
+        <v>0.2563552495281575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8409090638160706</v>
+        <v>0.8723404407501221</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7584415674209595</v>
+        <v>0.8372966051101685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7570934295654297</v>
+        <v>0.8268229365348816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7647058963775635</v>
+        <v>0.8339768052101135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0833228901028633</v>
+        <v>0.0898069441318512</v>
       </c>
       <c r="K5" t="n">
-        <v>15.4032609462738</v>
+        <v>30.07734775543213</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0836815071105957</v>
+        <v>0.06755642890930171</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0943303728103637</v>
+        <v>0.1619284009933471</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1044440174102783</v>
+        <v>0.1430262374877929</v>
       </c>
       <c r="O5" t="n">
-        <v>4.184075355529785</v>
+        <v>3.377821445465088</v>
       </c>
       <c r="P5" t="n">
-        <v>4.716518640518188</v>
+        <v>8.096420049667358</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.222200870513916</v>
+        <v>7.151311874389648</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-184310</t>
+          <t>20250731-015142</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>99.79649186134338</v>
+        <v>149.7587432861328</v>
       </c>
       <c r="D6" t="n">
-        <v>1.690000057220459</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1356823939118492</v>
+        <v>0.2582437221247416</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8602150678634644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7858520746231079</v>
+        <v>0.8483009934425354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7956715226173401</v>
+        <v>0.8407894968986511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7966858148574829</v>
+        <v>0.8456026315689087</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07481168955564491</v>
+        <v>0.1137223690748214</v>
       </c>
       <c r="K6" t="n">
-        <v>15.77063322067261</v>
+        <v>30.07850623130798</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08184924602508541</v>
+        <v>0.0731553173065185</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09463703155517569</v>
+        <v>0.1623418235778808</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1064108037948608</v>
+        <v>0.1300108766555786</v>
       </c>
       <c r="O6" t="n">
-        <v>4.092462301254272</v>
+        <v>3.657765865325928</v>
       </c>
       <c r="P6" t="n">
-        <v>4.731851577758789</v>
+        <v>8.117091178894043</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.320540189743042</v>
+        <v>6.500543832778931</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-184505</t>
+          <t>20250731-015431</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>196.4528479576111</v>
+        <v>38.94080662727356</v>
       </c>
       <c r="D2" t="n">
-        <v>5.360000133514404</v>
+        <v>6.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1043508633860011</v>
+        <v>0.1431720199493261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.760869562625885</v>
+        <v>0.7628865838050842</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6915887594223022</v>
+        <v>0.7347995042800903</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6826706528663635</v>
+        <v>0.7096307277679443</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6805040836334229</v>
+        <v>0.7088791728019714</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08511621505022041</v>
+        <v>0.1010807678103447</v>
       </c>
       <c r="K2" t="n">
-        <v>14.08759379386902</v>
+        <v>19.6290807723999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0677247810363769</v>
+        <v>0.0598593473434448</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0947965574264526</v>
+        <v>0.110951075553894</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0943818712234497</v>
+        <v>0.115096321105957</v>
       </c>
       <c r="O2" t="n">
-        <v>3.386239051818848</v>
+        <v>2.992967367172241</v>
       </c>
       <c r="P2" t="n">
-        <v>4.739827871322632</v>
+        <v>5.547553777694702</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.719093561172485</v>
+        <v>5.754816055297852</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-081457</t>
+          <t>20250627-160229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>109.8853189945221</v>
+        <v>31.10494256019592</v>
       </c>
       <c r="D3" t="n">
-        <v>5.349999904632568</v>
+        <v>6.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1052847837878239</v>
+        <v>0.146933092639364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7346938848495483</v>
+        <v>0.8478260636329651</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6806358098983765</v>
+        <v>0.7178549766540527</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6759123802185059</v>
+        <v>0.7055476307868958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6710622906684875</v>
+        <v>0.7062986493110657</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0951783210039138</v>
+        <v>0.0994821190834045</v>
       </c>
       <c r="K3" t="n">
-        <v>14.5590283870697</v>
+        <v>14.10325837135315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765637063980102</v>
+        <v>0.0607071161270141</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08697918891906729</v>
+        <v>0.1181252527236938</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0868967294692993</v>
+        <v>0.1207747030258178</v>
       </c>
       <c r="O3" t="n">
-        <v>3.828185319900513</v>
+        <v>3.035355806350708</v>
       </c>
       <c r="P3" t="n">
-        <v>4.348959445953369</v>
+        <v>5.906262636184692</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.344836473464966</v>
+        <v>6.038735151290894</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-081916</t>
+          <t>20250627-160421</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>87.46954298019409</v>
+        <v>62.48103547096253</v>
       </c>
       <c r="D4" t="n">
-        <v>5.349999904632568</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1056017916081314</v>
+        <v>0.1450334945693611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7741935253143311</v>
+        <v>0.8409090638160706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7072463631629944</v>
+        <v>0.760617733001709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6914893388748169</v>
+        <v>0.6640190482139587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6928895711898804</v>
+        <v>0.6656076312065125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0846295282244682</v>
+        <v>0.0873725637793541</v>
       </c>
       <c r="K4" t="n">
-        <v>14.72736620903015</v>
+        <v>19.34668064117432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0796511554718017</v>
+        <v>0.0598899126052856</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0870466184616088</v>
+        <v>0.1108040046691894</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08838952064514161</v>
+        <v>0.119082384109497</v>
       </c>
       <c r="O4" t="n">
-        <v>3.982557773590088</v>
+        <v>2.994495630264282</v>
       </c>
       <c r="P4" t="n">
-        <v>4.352330923080444</v>
+        <v>5.540200233459473</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.41947603225708</v>
+        <v>5.954119205474854</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-082207</t>
+          <t>20250627-160601</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>151.2278380393982</v>
+        <v>76.82273435592651</v>
       </c>
       <c r="D5" t="n">
-        <v>5.710000038146973</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1050729083900268</v>
+        <v>0.1453017875363554</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7647058963775635</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6933701634407043</v>
+        <v>0.7861799001693726</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6888731122016907</v>
+        <v>0.7447272539138794</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6886858940124512</v>
+        <v>0.7371512651443481</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0906932353973388</v>
+        <v>0.1666375398635864</v>
       </c>
       <c r="K5" t="n">
-        <v>8.890412330627441</v>
+        <v>19.35775232315063</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06657557964324951</v>
+        <v>0.0709398889541626</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0892628192901611</v>
+        <v>0.1116385126113891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0865938472747802</v>
+        <v>0.1151805782318115</v>
       </c>
       <c r="O5" t="n">
-        <v>3.328778982162476</v>
+        <v>3.54699444770813</v>
       </c>
       <c r="P5" t="n">
-        <v>4.463140964508057</v>
+        <v>5.581925630569458</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.329692363739014</v>
+        <v>5.759028911590576</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-082437</t>
+          <t>20250627-160817</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>159.5162649154663</v>
+        <v>59.37403678894043</v>
       </c>
       <c r="D6" t="n">
-        <v>5.360000133514404</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1061286760852971</v>
+        <v>0.1462286306639848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7727272510528564</v>
+        <v>0.8372092843055725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6642388701438904</v>
+        <v>0.7691247463226318</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6652110815048218</v>
+        <v>0.7260479331016541</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6588751077651978</v>
+        <v>0.7274085283279419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0768254399299621</v>
+        <v>0.0807815194129943</v>
       </c>
       <c r="K6" t="n">
-        <v>9.270299911499023</v>
+        <v>19.74275803565979</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0676875162124633</v>
+        <v>0.065195026397705</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08586668014526359</v>
+        <v>0.1070601511001587</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0948818254470825</v>
+        <v>0.1179280424118042</v>
       </c>
       <c r="O6" t="n">
-        <v>3.384375810623169</v>
+        <v>3.259751319885254</v>
       </c>
       <c r="P6" t="n">
-        <v>4.293334007263184</v>
+        <v>5.353007555007935</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.744091272354126</v>
+        <v>5.89640212059021</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-082809</t>
+          <t>20250627-161047</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C2" t="n">
-        <v>65.27910232543945</v>
+        <v>97.60025143623352</v>
       </c>
       <c r="D2" t="n">
-        <v>7.590000152587891</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1775395423173904</v>
+        <v>0.1341763613431641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8367347121238708</v>
+        <v>0.901098906993866</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7668638825416565</v>
+        <v>0.797650158405304</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7719504833221436</v>
+        <v>0.7751519083976746</v>
       </c>
       <c r="I2" t="n">
-        <v>0.766514778137207</v>
+        <v>0.7863818407058716</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0781708806753158</v>
+        <v>0.0686486735939979</v>
       </c>
       <c r="K2" t="n">
-        <v>29.93798279762268</v>
+        <v>15.97784423828125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09239889621734609</v>
+        <v>0.0821577024459838</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1716594409942627</v>
+        <v>0.09360282421112059</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1500326347351074</v>
+        <v>0.1054264307022094</v>
       </c>
       <c r="O2" t="n">
-        <v>4.61994481086731</v>
+        <v>4.107885122299194</v>
       </c>
       <c r="P2" t="n">
-        <v>8.582972049713135</v>
+        <v>4.68014121055603</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.501631736755371</v>
+        <v>5.271321535110474</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-102409</t>
+          <t>20250701-183539</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>98.91058778762816</v>
+        <v>88.69244909286499</v>
       </c>
       <c r="D3" t="n">
-        <v>7.510000228881836</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1768942616275839</v>
+        <v>0.1370802881974207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8409090638160706</v>
+        <v>0.8372092843055725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8641072511672974</v>
+        <v>0.8079951405525208</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8613861203193665</v>
+        <v>0.6564268469810486</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8615959882736206</v>
+        <v>0.6504064798355103</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0768109411001205</v>
+        <v>0.07012758404016491</v>
       </c>
       <c r="K3" t="n">
-        <v>30.25852537155152</v>
+        <v>15.55081009864807</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08869545936584471</v>
+        <v>0.0826942205429077</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1692540025711059</v>
+        <v>0.09040206909179679</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1484009170532226</v>
+        <v>0.0980330896377563</v>
       </c>
       <c r="O3" t="n">
-        <v>4.434772968292236</v>
+        <v>4.134711027145386</v>
       </c>
       <c r="P3" t="n">
-        <v>8.462700128555298</v>
+        <v>4.520103454589844</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.420045852661133</v>
+        <v>4.901654481887817</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-102639</t>
+          <t>20250701-183823</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>124.7675473690033</v>
+        <v>66.87515258789062</v>
       </c>
       <c r="D4" t="n">
-        <v>7.53000020980835</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1773750729700352</v>
+        <v>0.1350593031462976</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8913043737411499</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8533163070678711</v>
+        <v>0.7938271760940552</v>
       </c>
       <c r="H4" t="n">
-        <v>0.853960394859314</v>
+        <v>0.7900311350822449</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8526248931884766</v>
+        <v>0.7949367165565491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0875074565410614</v>
+        <v>0.0930452644824981</v>
       </c>
       <c r="K4" t="n">
-        <v>30.36792039871216</v>
+        <v>15.31155633926392</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0870620870590209</v>
+        <v>0.08335073947906491</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1669500732421875</v>
+        <v>0.1010682487487793</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1337246608734131</v>
+        <v>0.1061695051193237</v>
       </c>
       <c r="O4" t="n">
-        <v>4.35310435295105</v>
+        <v>4.167536973953247</v>
       </c>
       <c r="P4" t="n">
-        <v>8.347503662109375</v>
+        <v>5.053412437438965</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.686233043670654</v>
+        <v>5.308475255966187</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-102943</t>
+          <t>20250701-184057</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>78.33975791931152</v>
+        <v>49.76188492774963</v>
       </c>
       <c r="D5" t="n">
-        <v>7.599999904632568</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.177755178788961</v>
+        <v>0.1329132526774297</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.8409090638160706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8300192356109619</v>
+        <v>0.7584415674209595</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8260012865066528</v>
+        <v>0.7570934295654297</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8268229365348816</v>
+        <v>0.7647058963775635</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0841486528515815</v>
+        <v>0.0833228901028633</v>
       </c>
       <c r="K5" t="n">
-        <v>30.16714239120484</v>
+        <v>15.4032609462738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08182570934295651</v>
+        <v>0.0836815071105957</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1607763242721557</v>
+        <v>0.0943303728103637</v>
       </c>
       <c r="N5" t="n">
-        <v>0.141641879081726</v>
+        <v>0.1044440174102783</v>
       </c>
       <c r="O5" t="n">
-        <v>4.091285467147827</v>
+        <v>4.184075355529785</v>
       </c>
       <c r="P5" t="n">
-        <v>8.038816213607788</v>
+        <v>4.716518640518188</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.082093954086304</v>
+        <v>5.222200870513916</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-103322</t>
+          <t>20250701-184310</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C6" t="n">
-        <v>75.52639222145081</v>
+        <v>99.79649186134338</v>
       </c>
       <c r="D6" t="n">
-        <v>7.53000020980835</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1785959626237551</v>
+        <v>0.1356823939118492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8421052694320679</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8524590134620667</v>
+        <v>0.7858520746231079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8544183373451233</v>
+        <v>0.7956715226173401</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8529598712921143</v>
+        <v>0.7966858148574829</v>
       </c>
       <c r="J6" t="n">
-        <v>0.078239805996418</v>
+        <v>0.07481168955564491</v>
       </c>
       <c r="K6" t="n">
-        <v>30.27729439735413</v>
+        <v>15.77063322067261</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09191606521606439</v>
+        <v>0.08184924602508541</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1642709159851074</v>
+        <v>0.09463703155517569</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1406033849716186</v>
+        <v>0.1064108037948608</v>
       </c>
       <c r="O6" t="n">
-        <v>4.595803260803223</v>
+        <v>4.092462301254272</v>
       </c>
       <c r="P6" t="n">
-        <v>8.213545799255371</v>
+        <v>4.731851577758789</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.030169248580933</v>
+        <v>5.320540189743042</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-103614</t>
+          <t>20250701-184505</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
